--- a/event_registration_forms/037_quest_for_christ_event_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/037_quest_for_christ_event_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -823,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>age_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Age 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>event_time_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Event Time 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,12 +978,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'type',_'label':_'type',_'value':_'in-person',_'selected':_false}</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Type', 'label': 'Type', 'value': 'In-Person', 'selected': False}</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
@@ -995,29 +995,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'type',_'label':_'type',_'value':_'virtual',_'selected':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Type', 'label': 'Type', 'value': 'Virtual', 'selected': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'type',_'label':_'type',_'value':_'hybrid',_'selected':_false}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Type', 'label': 'Type', 'value': 'Hybrid', 'selected': False}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'method',_'label':_'cash',_'value':_'cash',_'selected':_false}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'method', 'label': 'Cash', 'value': 'Cash', 'selected': False}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'method',_'label':_'credit_card',_'value':_'credit_card',_'selected':_false}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'method', 'label': 'Credit Card', 'value': 'Credit card', 'selected': False}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1063,29 +1063,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'method',_'label':_'bank_transfer',_'value':_'bank_transfer',_'selected':_false}</t>
+          <t>online_bank_transfer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'method', 'label': 'Bank Transfer', 'value': 'Bank transfer', 'selected': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_19,_'name':_'method',_'label':_'online_bank_transfer',_'value':_'online_bank_transfer',_'selected':_false}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 19, 'name': 'method', 'label': 'Online Bank Transfer', 'value': 'Online Bank transfer', 'selected': False}</t>
+          <t>Online Bank Transfer</t>
         </is>
       </c>
     </row>
